--- a/inst/extdata/example_apx_drm_301/adam_spec.xlsx
+++ b/inst/extdata/example_apx_drm_301/adam_spec.xlsx
@@ -1,39 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" firstSheet="0" windowHeight="13125" windowWidth="13125" xWindow="0" yWindow="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="13125" windowHeight="13125" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ADSL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ADMH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ADCM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ADEX" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ADVS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ADAE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ADLB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ADEFF" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CODELISTS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADSL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMH" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADCM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADEX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADVS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADAE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADLB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADEFF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CODELISTS" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -52,12 +54,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -377,9 +446,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -426,14 +499,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F124"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2612,7 +2689,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ADCM_CMDOSFRQN</t>
+          <t>ADCM_CMDOSFRN</t>
         </is>
       </c>
       <c r="B80" t="e">
@@ -2635,7 +2712,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ADCM.CMDOSFRQN</t>
+          <t>ADCM.CMDOSFRN</t>
         </is>
       </c>
     </row>
@@ -3962,14 +4039,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M82"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4059,7 +4140,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -4118,7 +4199,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -4177,7 +4258,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -4236,7 +4317,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -4295,7 +4376,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -4354,7 +4435,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>100</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -4413,7 +4494,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -4472,7 +4553,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -4533,7 +4614,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -4592,7 +4673,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -4651,7 +4732,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -4712,7 +4793,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -4773,7 +4854,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>100</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -4834,7 +4915,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -4899,7 +4980,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>50</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -4960,7 +5041,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -5021,7 +5102,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -5082,7 +5163,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>200</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -5141,7 +5222,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -5200,7 +5281,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>200</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -5259,7 +5340,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -5318,7 +5399,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>200</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -5381,7 +5462,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -5444,7 +5525,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>200</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -5507,7 +5588,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -5570,7 +5651,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -5633,7 +5714,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -5696,7 +5777,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -5755,7 +5836,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -5818,7 +5899,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -5881,7 +5962,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>20</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -5940,7 +6021,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -5999,7 +6080,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>20</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -6058,7 +6139,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>20</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -6117,7 +6198,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>20</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -6176,7 +6257,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -6237,7 +6318,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -6296,7 +6377,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>200</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -6357,7 +6438,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>50</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -6418,7 +6499,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -6477,7 +6558,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -6536,7 +6617,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -6601,7 +6682,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -6666,7 +6747,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -6731,7 +6812,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -6796,7 +6877,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>20</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -6859,7 +6940,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>200</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -6920,7 +7001,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>100</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -6981,7 +7062,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>500</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -7042,7 +7123,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -7103,7 +7184,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -7164,7 +7245,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -7225,7 +7306,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -7288,7 +7369,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>50</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -7349,7 +7430,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -7410,7 +7491,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>50</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -7469,7 +7550,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -7528,7 +7609,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>50</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -7591,7 +7672,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -7654,7 +7735,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>50</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -7717,7 +7798,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -7780,7 +7861,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>20</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -7839,7 +7920,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>200</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -7900,7 +7981,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>200</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -7959,7 +8040,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -8020,7 +8101,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -8081,7 +8162,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>8</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -8142,7 +8223,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>40</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -8197,7 +8278,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>40</v>
       </c>
       <c r="F70" t="inlineStr">
@@ -8252,7 +8333,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -8307,7 +8388,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>8</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -8362,7 +8443,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E73">
+      <c r="E73" t="n">
         <v>8</v>
       </c>
       <c r="F73" t="inlineStr">
@@ -8417,7 +8498,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E74">
+      <c r="E74" t="n">
         <v>40</v>
       </c>
       <c r="F74" t="inlineStr">
@@ -8472,7 +8553,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E75">
+      <c r="E75" t="n">
         <v>40</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -8527,7 +8608,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E76">
+      <c r="E76" t="n">
         <v>8</v>
       </c>
       <c r="F76" t="inlineStr">
@@ -8582,7 +8663,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E77">
+      <c r="E77" t="n">
         <v>8</v>
       </c>
       <c r="F77" t="inlineStr">
@@ -8637,7 +8718,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E78">
+      <c r="E78" t="n">
         <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
@@ -8692,7 +8773,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E79">
+      <c r="E79" t="n">
         <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
@@ -8747,7 +8828,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E80">
+      <c r="E80" t="n">
         <v>8</v>
       </c>
       <c r="F80" t="inlineStr">
@@ -8802,7 +8883,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E81">
+      <c r="E81" t="n">
         <v>40</v>
       </c>
       <c r="F81" t="inlineStr">
@@ -8857,7 +8938,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E82">
+      <c r="E82" t="n">
         <v>40</v>
       </c>
       <c r="F82" t="inlineStr">
@@ -8894,14 +8975,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8991,7 +9076,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -9050,7 +9135,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -9109,7 +9194,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -9172,7 +9257,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -9231,7 +9316,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>50</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -9290,7 +9375,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -9349,7 +9434,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -9408,7 +9493,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -9467,7 +9552,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>100</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -9528,7 +9613,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -9589,7 +9674,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>20</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -9648,7 +9733,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -9707,7 +9792,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -9768,7 +9853,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>50</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -9827,7 +9912,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -9888,7 +9973,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -9947,7 +10032,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -10006,7 +10091,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -10067,7 +10152,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -10128,7 +10213,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -10189,7 +10274,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -10248,7 +10333,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -10307,7 +10392,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>200</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -10366,7 +10451,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -10425,7 +10510,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>200</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -10484,7 +10569,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -10543,7 +10628,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -10602,7 +10687,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -10665,7 +10750,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -10728,7 +10813,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -10789,7 +10874,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -10850,7 +10935,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>100</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -10911,7 +10996,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -10972,7 +11057,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>100</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -11033,7 +11118,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -11094,7 +11179,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -11155,7 +11240,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -11216,7 +11301,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -11277,7 +11362,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -11336,7 +11421,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -11397,7 +11482,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -11440,14 +11525,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -11537,7 +11626,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -11596,7 +11685,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -11655,7 +11744,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -11718,7 +11807,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -11777,7 +11866,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>200</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -11836,7 +11925,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -11899,7 +11988,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -11962,7 +12051,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -12025,7 +12114,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>200</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -12084,7 +12173,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>200</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -12143,7 +12232,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>200</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -12202,7 +12291,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>200</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -12265,7 +12354,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -12328,7 +12417,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>200</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -12389,7 +12478,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -12450,7 +12539,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -12509,7 +12598,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>50</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -12570,7 +12659,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>50</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -12618,7 +12707,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMDOSFRQN</t>
+          <t>CMDOSFRN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12631,7 +12720,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -12646,7 +12735,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ADCM_CMDOSFRQN</t>
+          <t>ADCM_CMDOSFRN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -12661,7 +12750,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Numeric companion to CMDOSFRQ. Integer code assigned per codelist ADCM_CMDOSFRQN.</t>
+          <t>Numeric companion to CMDOSFRQ. Integer code assigned per codelist ADCM_CMDOSFRN.</t>
         </is>
       </c>
       <c r="L20" t="e">
@@ -12692,7 +12781,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>200</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -12751,7 +12840,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -12810,7 +12899,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -12869,7 +12958,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>20</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -12930,7 +13019,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -12993,7 +13082,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -13056,7 +13145,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -13115,7 +13204,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -13174,7 +13263,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>200</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -13237,7 +13326,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -13300,7 +13389,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -13361,7 +13450,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -13422,7 +13511,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -13487,7 +13576,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -13552,7 +13641,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>200</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -13613,7 +13702,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>200</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -13674,7 +13763,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -13739,7 +13828,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -13798,7 +13887,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -13859,7 +13948,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>200</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -13920,7 +14009,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -13981,7 +14070,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>200</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -14042,7 +14131,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>20</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -14103,7 +14192,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>8</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -14166,7 +14255,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>200</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -14229,7 +14318,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>8</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -14288,7 +14377,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>8</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -14347,7 +14436,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -14406,7 +14495,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>8</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -14467,7 +14556,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -14504,14 +14593,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -14601,7 +14694,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -14660,7 +14753,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -14719,7 +14812,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -14782,7 +14875,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -14841,7 +14934,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -14900,7 +14993,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -14959,7 +15052,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -15020,7 +15113,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -15079,7 +15172,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>50</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -15140,7 +15233,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>50</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -15201,7 +15294,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>50</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -15262,7 +15355,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>50</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -15323,7 +15416,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>50</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -15384,7 +15477,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -15445,7 +15538,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>200</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -15504,7 +15597,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>200</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -15563,7 +15656,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -15622,7 +15715,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>19</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -15681,7 +15774,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>19</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -15740,7 +15833,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -15801,7 +15894,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -15864,7 +15957,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -15923,7 +16016,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -15986,7 +16079,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -16045,7 +16138,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -16108,7 +16201,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -16171,7 +16264,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -16230,7 +16323,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -16289,7 +16382,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -16348,7 +16441,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -16411,7 +16504,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -16474,7 +16567,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -16533,7 +16626,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -16592,7 +16685,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>200</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -16651,7 +16744,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>100</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -16712,7 +16805,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>8</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -16773,7 +16866,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -16832,7 +16925,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>200</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -16897,7 +16990,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>8</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -16962,7 +17055,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>200</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -17027,7 +17120,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -17092,7 +17185,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>8</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -17155,7 +17248,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>8</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -17218,7 +17311,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -17283,7 +17376,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -17344,7 +17437,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -17409,7 +17502,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>200</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -17472,7 +17565,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>50</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -17529,7 +17622,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>200</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -17592,7 +17685,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -17655,7 +17748,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -17716,7 +17809,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -17777,7 +17870,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -17838,7 +17931,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -17899,7 +17992,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -17960,7 +18053,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -18021,7 +18114,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>40</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -18076,7 +18169,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -18131,7 +18224,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>40</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -18168,14 +18261,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -18265,7 +18362,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -18322,7 +18419,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -18383,7 +18480,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -18444,7 +18541,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -18505,7 +18602,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>200</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -18564,7 +18661,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -18623,7 +18720,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -18682,7 +18779,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -18741,7 +18838,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -18800,7 +18897,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -18859,7 +18956,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -18918,7 +19015,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -18979,7 +19076,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -19040,7 +19137,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -19097,7 +19194,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>200</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -19158,7 +19255,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -19219,7 +19316,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -19276,7 +19373,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>200</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -19337,7 +19434,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -19398,7 +19495,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -19459,7 +19556,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>200</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -19520,7 +19617,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>200</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -19577,7 +19674,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -19636,7 +19733,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -19693,7 +19790,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>200</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -19750,7 +19847,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -19807,7 +19904,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -19864,7 +19961,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>200</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -19927,7 +20024,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -19990,7 +20087,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>200</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -20053,7 +20150,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -20112,7 +20209,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -20173,7 +20270,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -20234,7 +20331,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -20293,7 +20390,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -20354,7 +20451,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>8</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -20415,7 +20512,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -20476,7 +20573,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -20537,7 +20634,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>20</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -20594,7 +20691,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>40</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -20655,7 +20752,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -20716,7 +20813,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>40</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -20777,7 +20874,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>40</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -20838,7 +20935,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>40</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -20899,7 +20996,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -20962,7 +21059,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>8</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -21019,7 +21116,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>8</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -21076,7 +21173,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>8</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -21133,7 +21230,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -21190,7 +21287,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -21247,7 +21344,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -21304,7 +21401,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -21361,7 +21458,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -21422,7 +21519,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>40</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -21483,7 +21580,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -21548,7 +21645,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>200</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -21596,7 +21693,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BASECAT1N</t>
+          <t>BASECA1N</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -21609,7 +21706,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -21635,7 +21732,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BASECAT1N is the numeric representation of BASECAT1, assigned via a sponsor-defined lookup to facilitate ordering of baseline category values. See codelist ADVS_BASECAT1.</t>
+          <t>BASECA1N is the numeric representation of BASECAT1, assigned via a sponsor-defined lookup to facilitate ordering of baseline category values. See codelist ADVS_BASECAT1.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -21670,7 +21767,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>200</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -21718,7 +21815,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AVALCAT1N</t>
+          <t>AVALCA1N</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -21731,7 +21828,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -21757,7 +21854,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>AVALCAT1N is the numeric representation of AVALCAT1, assigned via a sponsor-defined lookup to facilitate ordering. See codelist ADVS_AVALCAT1.</t>
+          <t>AVALCA1N is the numeric representation of AVALCAT1, assigned via a sponsor-defined lookup to facilitate ordering. See codelist ADVS_AVALCAT1.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -21792,7 +21889,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>20</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -21853,7 +21950,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>200</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -21914,7 +22011,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>20</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -21957,14 +22054,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M76"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -22054,7 +22155,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -22113,7 +22214,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -22172,7 +22273,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -22231,7 +22332,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -22290,7 +22391,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -22349,7 +22450,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -22408,7 +22509,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -22467,7 +22568,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -22526,7 +22627,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>200</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -22585,7 +22686,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>200</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -22646,7 +22747,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -22707,7 +22808,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>200</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -22768,7 +22869,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -22829,7 +22930,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>200</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -22890,7 +22991,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>20</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -22951,7 +23052,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>200</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -23010,7 +23111,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -23069,7 +23170,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -23128,7 +23229,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -23187,7 +23288,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -23246,7 +23347,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -23305,7 +23406,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>40</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -23364,7 +23465,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>20</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -23425,7 +23526,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -23486,7 +23587,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -23547,7 +23648,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -23608,7 +23709,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>40</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -23669,7 +23770,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -23734,7 +23835,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>40</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -23793,7 +23894,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -23854,7 +23955,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -23919,7 +24020,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>40</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -23978,7 +24079,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -24041,7 +24142,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>10</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -24102,7 +24203,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -24165,7 +24266,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -24228,7 +24329,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>20</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -24289,7 +24390,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -24352,7 +24453,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -24415,7 +24516,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -24478,7 +24579,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>100</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -24539,7 +24640,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -24604,7 +24705,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>100</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -24667,7 +24768,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>100</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -24730,7 +24831,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>200</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -24793,7 +24894,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -24854,7 +24955,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -24915,7 +25016,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -24976,7 +25077,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -25035,7 +25136,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -25094,7 +25195,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -25153,7 +25254,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -25212,7 +25313,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -25271,7 +25372,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -25336,7 +25437,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>40</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -25401,7 +25502,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -25466,7 +25567,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -25529,7 +25630,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>40</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -25592,7 +25693,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>2</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -25653,7 +25754,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>200</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -25714,7 +25815,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -25775,7 +25876,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>200</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -25836,7 +25937,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>8</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -25897,7 +25998,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>200</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -25962,7 +26063,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -26021,7 +26122,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -26080,7 +26181,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>8</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -26139,7 +26240,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>40</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -26200,7 +26301,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
@@ -26261,7 +26362,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>10</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -26322,7 +26423,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>8</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -26383,7 +26484,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E73">
+      <c r="E73" t="n">
         <v>100</v>
       </c>
       <c r="F73" t="inlineStr">
@@ -26444,7 +26545,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E74">
+      <c r="E74" t="n">
         <v>8</v>
       </c>
       <c r="F74" t="inlineStr">
@@ -26505,7 +26606,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E75">
+      <c r="E75" t="n">
         <v>100</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -26566,7 +26667,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E76">
+      <c r="E76" t="n">
         <v>8</v>
       </c>
       <c r="F76" t="inlineStr">
@@ -26609,14 +26710,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -26706,7 +26811,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -26765,7 +26870,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -26824,7 +26929,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -26887,7 +26992,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -26946,7 +27051,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>50</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -27005,7 +27110,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>50</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -27064,7 +27169,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -27123,7 +27228,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -27182,7 +27287,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>50</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -27243,7 +27348,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>50</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -27302,7 +27407,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -27361,7 +27466,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>200</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -27420,7 +27525,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -27485,7 +27590,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -27546,7 +27651,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>200</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -27605,7 +27710,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -27664,7 +27769,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>200</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -27723,7 +27828,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>50</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -27782,7 +27887,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>200</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -27841,7 +27946,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>50</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -27900,7 +28005,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -27959,7 +28064,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>200</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -28018,7 +28123,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -28077,7 +28182,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -28136,7 +28241,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -28197,7 +28302,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -28258,7 +28363,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -28323,7 +28428,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -28386,7 +28491,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>200</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -28445,7 +28550,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -28504,7 +28609,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>200</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -28567,7 +28672,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -28632,7 +28737,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>200</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -28695,7 +28800,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -28760,7 +28865,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -28819,7 +28924,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>20</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -28878,7 +28983,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -28937,7 +29042,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -28996,7 +29101,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>8</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -29055,7 +29160,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -29114,7 +29219,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -29173,7 +29278,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>50</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -29232,7 +29337,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>50</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -29291,7 +29396,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>10</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -29352,7 +29457,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>10</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -29413,7 +29518,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>10</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -29474,7 +29579,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -29539,7 +29644,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -29604,7 +29709,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>2</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -29669,7 +29774,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>30</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -29732,7 +29837,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -29795,7 +29900,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -29860,7 +29965,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -29921,7 +30026,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>20</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -29980,7 +30085,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>200</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -30039,7 +30144,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>200</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -30098,7 +30203,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -30159,7 +30264,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>200</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -30218,7 +30323,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -30279,7 +30384,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -30338,7 +30443,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -30397,7 +30502,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -30456,7 +30561,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>20</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -30517,7 +30622,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -30578,7 +30683,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -30639,7 +30744,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -30700,7 +30805,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>200</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -30761,7 +30866,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>8</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -30822,7 +30927,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>200</v>
       </c>
       <c r="F70" t="inlineStr">
@@ -30883,7 +30988,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -30944,7 +31049,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>8</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -30985,14 +31090,18 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -31082,7 +31191,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -31139,7 +31248,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>50</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -31196,7 +31305,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -31253,7 +31362,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -31310,7 +31419,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -31369,7 +31478,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>40</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -31434,7 +31543,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -31495,7 +31604,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -31556,7 +31665,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -31617,7 +31726,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>100</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -31678,7 +31787,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -31739,7 +31848,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>60</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -31800,7 +31909,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -31861,7 +31970,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>40</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -31922,7 +32031,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>200</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -31981,7 +32090,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -32040,7 +32149,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>200</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -32099,7 +32208,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -32158,7 +32267,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>200</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -32217,7 +32326,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -32276,7 +32385,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>200</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -32335,7 +32444,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -32394,7 +32503,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -32453,7 +32562,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -32514,7 +32623,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -32573,7 +32682,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -32636,7 +32745,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -32697,7 +32806,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>200</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -32758,7 +32867,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -32819,7 +32928,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -32876,7 +32985,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>200</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -32933,7 +33042,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -32990,7 +33099,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>200</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -33047,7 +33156,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -33104,7 +33213,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -33161,7 +33270,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -33220,7 +33329,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -33279,7 +33388,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>200</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -33338,7 +33447,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>200</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -33401,7 +33510,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -33464,7 +33573,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -33525,7 +33634,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>8</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -33584,7 +33693,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>40</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -33647,7 +33756,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -33710,7 +33819,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -33773,7 +33882,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -33836,7 +33945,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>40</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -33897,7 +34006,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -33960,7 +34069,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -34019,7 +34128,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -34080,7 +34189,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>8</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -34141,7 +34250,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>40</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -34202,7 +34311,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -34263,7 +34372,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -34324,7 +34433,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -34385,7 +34494,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -34442,7 +34551,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>10</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -34499,7 +34608,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -34556,7 +34665,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>100</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -34604,7 +34713,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BASECAT1N</t>
+          <t>BASECA1N</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -34617,7 +34726,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -34643,7 +34752,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>BASECAT1N is the numeric code for BASECAT1 assigned to facilitate ordered display of baseline category subgroups. There is a one-to-one relationship between BASECAT1 and BASECAT1N within each PARAM.</t>
+          <t>BASECA1N is the numeric code for BASECAT1 assigned to facilitate ordered display of baseline category subgroups. There is a one-to-one relationship between BASECAT1 and BASECA1N within each PARAM.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -34653,7 +34762,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>BASECAT1N assignment must be confirmed after BASECAT1 category definitions are finalized per the SAP.</t>
+          <t>BASECA1N assignment must be confirmed after BASECAT1 category definitions are finalized per the SAP.</t>
         </is>
       </c>
     </row>
@@ -34678,7 +34787,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>100</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -34726,7 +34835,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AVALCAT1N</t>
+          <t>AVALCA1N</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -34739,7 +34848,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -34765,7 +34874,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>AVALCAT1N is the numeric code for AVALCAT1, assigned to facilitate ordered display. There is a one-to-one relationship between AVALCAT1 and AVALCAT1N within each PARAM.</t>
+          <t>AVALCA1N is the numeric code for AVALCAT1, assigned to facilitate ordered display. There is a one-to-one relationship between AVALCAT1 and AVALCA1N within each PARAM.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -34775,7 +34884,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>AVALCAT1N assignment must be confirmed after AVALCAT1 category definitions are finalized per the SAP.</t>
+          <t>AVALCA1N assignment must be confirmed after AVALCAT1 category definitions are finalized per the SAP.</t>
         </is>
       </c>
     </row>
@@ -34800,7 +34909,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -34863,7 +34972,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -34926,7 +35035,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -34985,7 +35094,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -35048,7 +35157,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -35111,7 +35220,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -35174,7 +35283,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
@@ -35237,7 +35346,7 @@
           <t>text</t>
         </is>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -35282,6 +35391,6 @@
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/inst/extdata/example_apx_drm_301/adam_spec.xlsx
+++ b/inst/extdata/example_apx_drm_301/adam_spec.xlsx
@@ -4049,7 +4049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16"/>
   <sheetData>
     <row r="1">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CROSSFL</t>
+          <t>STRAT1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Crossover Flag</t>
+          <t>Stratification Factor 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7319,22 +7319,20 @@
           <t>Perm</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
+      <c r="H54" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I54" t="e">
         <v>#N/A</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Flag for placebo subjects who crossed over at Week 16 and were re-randomized. Set to 'Y' if subject was originally randomized to placebo (TRT01P='Placebo') and has a DS record for crossover/re-randomization at Week 16. Used in T-14-1-1.</t>
+          <t>Stratification factor 1: baseline vIGA-AD severity (3 vs 4). Derived from randomization strata records or SUPPDM.QVAL where QNAM='VIGABASE' (or equivalent). Values: '3' (moderate) or '4' (severe). Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Crossover flag set to 'Y' for placebo subjects re-randomized at Week 16 crossover point. Derived from DS domain records (DSDECOD indicating re-randomization) combined with original planned treatment being Placebo. Uses codelist NY.</t>
+          <t>Stratification factor 1 representing baseline vIGA-AD severity (3 or 4) from randomization strata. Derived from SUPPDM or randomization database. Uses sponsor-defined codelist ADSL_STRAT1.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -7344,7 +7342,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>DS domain variables (DSDECOD for crossover/re-randomization) not RAG-verified. Programmer must confirm DS domain coding for the Week 16 crossover event and re-randomization records.</t>
+          <t>SUPPDM variables not RAG-verified. Programmer must confirm the QNAM value used for baseline vIGA-AD in SUPPDM (e.g., QNAM='VIGABASE') or identify the randomization stratum dataset source.</t>
         </is>
       </c>
     </row>
@@ -7356,21 +7354,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STRAT1</t>
+          <t>STRAT1N</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stratification Factor 1</t>
+          <t>Stratification Factor 1 (N)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7390,12 +7388,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Stratification factor 1: baseline vIGA-AD severity (3 vs 4). Derived from randomization strata records or SUPPDM.QVAL where QNAM='VIGABASE' (or equivalent). Values: '3' (moderate) or '4' (severe). Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
+          <t>Numeric code for STRAT1. 3=vIGA-AD score 3; 4=vIGA-AD score 4. See codelist ADSL_STRAT1N.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Stratification factor 1 representing baseline vIGA-AD severity (3 or 4) from randomization strata. Derived from SUPPDM or randomization database. Uses sponsor-defined codelist ADSL_STRAT1.</t>
+          <t>Numeric representation of STRAT1 for sorting. 3=Baseline vIGA-AD score 3; 4=Baseline vIGA-AD score 4. Uses sponsor-defined codelist ADSL_STRAT1N.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -7405,7 +7403,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>SUPPDM variables not RAG-verified. Programmer must confirm the QNAM value used for baseline vIGA-AD in SUPPDM (e.g., QNAM='VIGABASE') or identify the randomization stratum dataset source.</t>
+          <t>Dependent on STRAT1 derivation which requires SUPPDM source confirmation. Numeric code assignment must be confirmed with sponsor.</t>
         </is>
       </c>
     </row>
@@ -7417,21 +7415,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STRAT1N</t>
+          <t>STRAT2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stratification Factor 1 (N)</t>
+          <t>Stratification Factor 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7446,28 +7444,26 @@
       <c r="H56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>DM.AGE</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Numeric code for STRAT1. 3=vIGA-AD score 3; 4=vIGA-AD score 4. See codelist ADSL_STRAT1N.</t>
+          <t>Stratification factor 2: age group (Adolescent vs Adult). Derived from DM.AGE: 'Adolescent' if AGE &lt; 18; 'Adult' if AGE &gt;= 18. Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Numeric representation of STRAT1 for sorting. 3=Baseline vIGA-AD score 3; 4=Baseline vIGA-AD score 4. Uses sponsor-defined codelist ADSL_STRAT1N.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Dependent on STRAT1 derivation which requires SUPPDM source confirmation. Numeric code assignment must be confirmed with sponsor.</t>
-        </is>
+          <t>Stratification factor 2 representing age group derived from DM.AGE: 'Adolescent' if AGE&lt;18; 'Adult' if AGE&gt;=18. Used for CMH test stratification in efficacy analyses. Uses sponsor-defined codelist ADSL_STRAT2.</t>
+        </is>
+      </c>
+      <c r="L56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M56" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="57">
@@ -7478,21 +7474,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STRAT2</t>
+          <t>STRAT2N</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stratification Factor 2</t>
+          <t>Stratification Factor 2 (N)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7514,12 +7510,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Stratification factor 2: age group (Adolescent vs Adult). Derived from DM.AGE: 'Adolescent' if AGE &lt; 18; 'Adult' if AGE &gt;= 18. Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
+          <t>Numeric code for STRAT2. 1=Adolescent (AGE &lt; 18); 2=Adult (AGE &gt;= 18). See codelist ADSL_STRAT2N.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Stratification factor 2 representing age group derived from DM.AGE: 'Adolescent' if AGE&lt;18; 'Adult' if AGE&gt;=18. Used for CMH test stratification in efficacy analyses. Uses sponsor-defined codelist ADSL_STRAT2.</t>
+          <t>Numeric representation of STRAT2 for sorting. 1=Adolescent (AGE&lt;18); 2=Adult (AGE&gt;=18). Uses sponsor-defined codelist ADSL_STRAT2N.</t>
         </is>
       </c>
       <c r="L57" t="e">
@@ -7537,21 +7533,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STRAT2N</t>
+          <t>STRAT3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stratification Factor 2 (N)</t>
+          <t>Stratification Factor 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7568,24 +7564,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DM.AGE</t>
+          <t>DM.COUNTRY</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Numeric code for STRAT2. 1=Adolescent (AGE &lt; 18); 2=Adult (AGE &gt;= 18). See codelist ADSL_STRAT2N.</t>
+          <t>Stratification factor 3: geographic region. Derived from DM.COUNTRY mapped to regions (e.g., North America, Europe, Asia-Pacific, Rest of World). Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Numeric representation of STRAT2 for sorting. 1=Adolescent (AGE&lt;18); 2=Adult (AGE&gt;=18). Uses sponsor-defined codelist ADSL_STRAT2N.</t>
-        </is>
-      </c>
-      <c r="L58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M58" t="e">
-        <v>#N/A</v>
+          <t>Stratification factor 3 representing geographic region derived from DM.COUNTRY mapping to study-defined regions. Used for CMH test stratification in efficacy analyses. Uses sponsor-defined codelist ADSL_STRAT3.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Region grouping algorithm from DM.COUNTRY must be confirmed with sponsor. Randomization stratum for region may differ from post-hoc grouping; programmer should check if region stratum is stored in SUPPDM.</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -7596,21 +7596,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STRAT3</t>
+          <t>STRAT3N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stratification Factor 3</t>
+          <t>Stratification Factor 3 (N)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7632,12 +7632,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Stratification factor 3: geographic region. Derived from DM.COUNTRY mapped to regions (e.g., North America, Europe, Asia-Pacific, Rest of World). Used in CMH test for primary endpoint analysis (T-14-2-1).</t>
+          <t>Numeric code for STRAT3. Numeric mapping of geographic region. See codelist ADSL_STRAT3N.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Stratification factor 3 representing geographic region derived from DM.COUNTRY mapping to study-defined regions. Used for CMH test stratification in efficacy analyses. Uses sponsor-defined codelist ADSL_STRAT3.</t>
+          <t>Numeric representation of STRAT3 (geographic region) for sorting. Uses sponsor-defined codelist ADSL_STRAT3N.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Region grouping algorithm from DM.COUNTRY must be confirmed with sponsor. Randomization stratum for region may differ from post-hoc grouping; programmer should check if region stratum is stored in SUPPDM.</t>
+          <t>Dependent on STRAT3 region grouping algorithm which must be confirmed with sponsor.</t>
         </is>
       </c>
     </row>
@@ -7659,21 +7659,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>STRAT3N</t>
+          <t>REGION1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stratification Factor 3 (N)</t>
+          <t>Geographic Region 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Numeric code for STRAT3. Numeric mapping of geographic region. See codelist ADSL_STRAT3N.</t>
+          <t>Geographic region derived from DM.COUNTRY. Countries mapped to regions (e.g., 'North America', 'Europe', 'Asia-Pacific', 'Rest of World'). Used in demographic tables (T-14-1-2) and CMH stratification.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Numeric representation of STRAT3 (geographic region) for sorting. Uses sponsor-defined codelist ADSL_STRAT3N.</t>
+          <t>Geographic region derived from DM.COUNTRY using sponsor-defined country-to-region mapping. Uses sponsor-defined codelist ADSL_REGION1.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Dependent on STRAT3 region grouping algorithm which must be confirmed with sponsor.</t>
+          <t>Country-to-region mapping algorithm must be confirmed with sponsor. The exact region groupings need to be defined in the SAP or programming specifications.</t>
         </is>
       </c>
     </row>
@@ -7722,21 +7722,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>REGION1</t>
+          <t>REGION1N</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Geographic Region 1</t>
+          <t>Geographic Region 1 (N)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7758,12 +7758,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Geographic region derived from DM.COUNTRY. Countries mapped to regions (e.g., 'North America', 'Europe', 'Asia-Pacific', 'Rest of World'). Used in demographic tables (T-14-1-2) and CMH stratification.</t>
+          <t>Numeric code for REGION1. Numeric representation of geographic region for sorting. See codelist ADSL_REGION1N.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Geographic region derived from DM.COUNTRY using sponsor-defined country-to-region mapping. Uses sponsor-defined codelist ADSL_REGION1.</t>
+          <t>Numeric representation of REGION1 for sorting. Uses sponsor-defined codelist ADSL_REGION1N.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Country-to-region mapping algorithm must be confirmed with sponsor. The exact region groupings need to be defined in the SAP or programming specifications.</t>
+          <t>Dependent on REGION1 mapping algorithm which must be confirmed with sponsor.</t>
         </is>
       </c>
     </row>
@@ -7785,25 +7785,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>REGION1N</t>
+          <t>BRTHDTC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Geographic Region 1 (N)</t>
+          <t>Date/Time of Birth</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Predecessor</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7816,28 +7816,24 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DM.COUNTRY</t>
+          <t>DM.BRTHDTC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Numeric code for REGION1. Numeric representation of geographic region for sorting. See codelist ADSL_REGION1N.</t>
+          <t>Copied directly from DM.BRTHDTC. ISO 8601 date/time of birth.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Numeric representation of REGION1 for sorting. Uses sponsor-defined codelist ADSL_REGION1N.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Dependent on REGION1 mapping algorithm which must be confirmed with sponsor.</t>
-        </is>
+          <t>Date/time of birth copied from DM.BRTHDTC in ISO 8601 format.</t>
+        </is>
+      </c>
+      <c r="L62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M62" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="63">
@@ -7848,12 +7844,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BRTHDTC</t>
+          <t>ARMNRS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Date/Time of Birth</t>
+          <t>Reason Arm Not Assigned</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7862,7 +7858,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7874,22 +7870,24 @@
           <t>Perm</t>
         </is>
       </c>
-      <c r="H63" t="e">
-        <v>#N/A</v>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ADSL_ARMNRS</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DM.BRTHDTC</t>
+          <t>DM.ARMNRS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Copied directly from DM.BRTHDTC. ISO 8601 date/time of birth.</t>
+          <t>Copied directly from DM.ARMNRS. Describes the reason a subject was not assigned to an arm (e.g., screen failure).</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Date/time of birth copied from DM.BRTHDTC in ISO 8601 format.</t>
+          <t>Reason arm not assigned copied from DM.ARMNRS. Populated for subjects with missing ARMCD.</t>
         </is>
       </c>
       <c r="L63" t="e">
@@ -7907,12 +7905,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ARMNRS</t>
+          <t>ACTARMUD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reason Arm Not Assigned</t>
+          <t>Description of Unplanned Actual Arm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7933,24 +7931,22 @@
           <t>Perm</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>ADSL_ARMNRS</t>
-        </is>
+      <c r="H64" t="e">
+        <v>#N/A</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DM.ARMNRS</t>
+          <t>DM.ACTARMUD</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Copied directly from DM.ARMNRS. Describes the reason a subject was not assigned to an arm (e.g., screen failure).</t>
+          <t>Copied directly from DM.ACTARMUD. Describes the actual arm if it was unplanned.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Reason arm not assigned copied from DM.ARMNRS. Populated for subjects with missing ARMCD.</t>
+          <t>Description of unplanned actual arm copied from DM.ACTARMUD.</t>
         </is>
       </c>
       <c r="L64" t="e">
@@ -7968,48 +7964,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ACTARMUD</t>
+          <t>AGEUN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Description of Unplanned Actual Arm</t>
+          <t>Age Units (N)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Predecessor</t>
+          <t>Derived</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Perm</t>
-        </is>
-      </c>
-      <c r="H65" t="e">
-        <v>#N/A</v>
+          <t>Req</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ADSL_AGEUN</t>
+        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DM.ACTARMUD</t>
+          <t>DM.AGEU</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Copied directly from DM.ACTARMUD. Describes the actual arm if it was unplanned.</t>
+          <t>Numeric code for AGEU. See codelist ADSL_AGEUN.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Description of unplanned actual arm copied from DM.ACTARMUD.</t>
+          <t>Numeric version of AGEU. Assigned from ADSL_AGEUN codelist numeric decode.</t>
         </is>
       </c>
       <c r="L65" t="e">
@@ -8027,12 +8025,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AGEUN</t>
+          <t>COUNTRYN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Age Units (N)</t>
+          <t>Country (N)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8050,27 +8048,27 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Req</t>
+          <t>Perm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ADSL_AGEUN</t>
+          <t>COUNTRYN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DM.AGEU</t>
+          <t>DM.COUNTRY</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Numeric code for AGEU. See codelist ADSL_AGEUN.</t>
+          <t>Numeric code for COUNTRY. See codelist COUNTRYN.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Numeric version of AGEU. Assigned from ADSL_AGEUN codelist numeric decode.</t>
+          <t>Numeric version of COUNTRY. Assigned from COUNTRYN codelist numeric decode.</t>
         </is>
       </c>
       <c r="L66" t="e">
@@ -8088,12 +8086,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COUNTRYN</t>
+          <t>ARMNRSN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Country (N)</t>
+          <t>Reason Arm Not Assigned (N)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8116,22 +8114,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>COUNTRYN</t>
+          <t>ADSL_ARMNRSN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DM.COUNTRY</t>
+          <t>DM.ARMNRS</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Numeric code for COUNTRY. See codelist COUNTRYN.</t>
+          <t>Numeric code for ARMNRS. See codelist ADSL_ARMNRSN.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Numeric version of COUNTRY. Assigned from COUNTRYN codelist numeric decode.</t>
+          <t>Numeric version of ARMNRS. Assigned from ADSL_ARMNRSN codelist numeric decode.</t>
         </is>
       </c>
       <c r="L67" t="e">
@@ -8149,21 +8147,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ARMNRSN</t>
+          <t>REGION</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reason Arm Not Assigned (N)</t>
+          <t>Geographic Region</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8175,25 +8173,19 @@
           <t>Perm</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>ADSL_ARMNRSN</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>DM.ARMNRS</t>
-        </is>
+      <c r="H68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I68" t="e">
+        <v>#N/A</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Numeric code for ARMNRS. See codelist ADSL_ARMNRSN.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Numeric version of ARMNRS. Assigned from ADSL_ARMNRSN codelist numeric decode.</t>
-        </is>
+          <t>Simulated for the APX-DRM-301 training example.</t>
+        </is>
+      </c>
+      <c r="K68" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L68" t="e">
         <v>#N/A</v>
@@ -8210,12 +8202,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>REGION</t>
+          <t>DCSREASN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Geographic Region</t>
+          <t>Discontinuation Reason</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8265,21 +8257,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DCSREASN</t>
+          <t>WEIGHT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Discontinuation Reason</t>
+          <t>Body Weight (kg)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8320,12 +8312,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WEIGHT</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Body Weight (kg)</t>
+          <t>Body Mass Index (kg/m2)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8375,17 +8367,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>EASIBL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Body Mass Index (kg/m2)</t>
+          <t>Baseline EASI Total Score</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -8430,21 +8422,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EASIBL</t>
+          <t>EASIBLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baseline EASI Total Score</t>
+          <t>Baseline EASI Severity Category</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8485,12 +8477,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EASIBLC</t>
+          <t>IGABLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Baseline EASI Severity Category</t>
+          <t>Baseline vIGA-AD Category</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8540,21 +8532,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IGABLC</t>
+          <t>BSABL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Baseline vIGA-AD Category</t>
+          <t>Baseline % BSA Affected</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8595,17 +8587,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BSABL</t>
+          <t>WPNRSBL</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baseline % BSA Affected</t>
+          <t>Baseline WP-NRS Score</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8650,12 +8642,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WPNRSBL</t>
+          <t>POEMBL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baseline WP-NRS Score</t>
+          <t>Baseline POEM Total Score</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8705,12 +8697,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>POEMBL</t>
+          <t>DLQIBL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Baseline POEM Total Score</t>
+          <t>Baseline DLQI/CDLQI Total Score</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8760,17 +8752,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DLQIBL</t>
+          <t>ADDUR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Baseline DLQI/CDLQI Total Score</t>
+          <t>Duration of Atopic Dermatitis (years)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>float</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8815,21 +8807,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADDUR</t>
+          <t>ATOPCMB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Duration of Atopic Dermatitis (years)</t>
+          <t>Atopic Comorbidities Present</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8870,12 +8862,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ATOPCMB</t>
+          <t>PRSYSTAD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atopic Comorbidities Present</t>
+          <t>Prior Systemic Therapy for AD</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8914,61 +8906,6 @@
         <v>#N/A</v>
       </c>
       <c r="M81" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PRSYSTAD</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Prior Systemic Therapy for AD</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>40</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Derived</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Perm</t>
-        </is>
-      </c>
-      <c r="H82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Simulated for the APX-DRM-301 training example.</t>
-        </is>
-      </c>
-      <c r="K82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M82" t="e">
         <v>#N/A</v>
       </c>
     </row>
